--- a/event_feedback_forms/015_event_food_and_beverage_services_questionnaire--event_feedback_forms.xlsx
+++ b/event_feedback_forms/015_event_food_and_beverage_services_questionnaire--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
